--- a/data/faculty.xlsx
+++ b/data/faculty.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRANAV\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C97E62-D742-4439-BD5B-0133B51BD87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13290"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="14496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -203,8 +204,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,16 +544,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -563,7 +564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>9240</v>
       </c>
@@ -574,7 +575,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5254</v>
       </c>
@@ -585,7 +586,10 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>9378</v>
+      </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -593,7 +597,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4210</v>
       </c>
@@ -604,7 +608,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>9228</v>
       </c>
@@ -615,7 +619,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1102</v>
       </c>
@@ -626,7 +630,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>9300</v>
       </c>
@@ -637,7 +641,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3215</v>
       </c>
@@ -648,7 +652,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1112</v>
       </c>
@@ -659,7 +663,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25346</v>
       </c>
@@ -670,7 +674,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>5730</v>
       </c>
@@ -681,7 +685,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>16049</v>
       </c>
@@ -692,7 +696,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25418</v>
       </c>
@@ -703,7 +707,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>3319</v>
       </c>
@@ -714,7 +718,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>24373</v>
       </c>
@@ -725,7 +729,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1606</v>
       </c>
@@ -736,7 +740,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1609</v>
       </c>
@@ -747,7 +751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26067</v>
       </c>
@@ -758,7 +762,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>9363</v>
       </c>
@@ -769,7 +773,10 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>24282</v>
+      </c>
       <c r="B21" t="s">
         <v>19</v>
       </c>
@@ -777,7 +784,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>24280</v>
       </c>
@@ -788,7 +795,10 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>5200</v>
+      </c>
       <c r="B23" t="s">
         <v>21</v>
       </c>
@@ -796,7 +806,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1505</v>
       </c>
@@ -807,7 +817,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>11</v>
       </c>
@@ -815,7 +825,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24287</v>
       </c>
@@ -826,7 +836,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3497</v>
       </c>
@@ -837,7 +847,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>4137</v>
       </c>
@@ -848,7 +858,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>27</v>
       </c>

--- a/data/faculty.xlsx
+++ b/data/faculty.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
   <si>
     <t>Employee Code</t>
   </si>
@@ -196,6 +196,36 @@
   </si>
   <si>
     <t>RIMT_FDP_726_029</t>
+  </si>
+  <si>
+    <t>DEERAJ GARG</t>
+  </si>
+  <si>
+    <t>RIMT_FDP_726_030</t>
+  </si>
+  <si>
+    <t>DEEPSHIKA</t>
+  </si>
+  <si>
+    <t>RIMT_FDP_726_031</t>
+  </si>
+  <si>
+    <t>SIMRANJEET KAUR</t>
+  </si>
+  <si>
+    <t>RIMT_FDP_726_032</t>
+  </si>
+  <si>
+    <t>NAGMA KUMARI</t>
+  </si>
+  <si>
+    <t>RIMT_FDP_726_033</t>
+  </si>
+  <si>
+    <t>ANJALI</t>
+  </si>
+  <si>
+    <t>RIMT_FDP_726_034</t>
   </si>
 </sst>
 </file>
@@ -790,6 +820,9 @@
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="3">
+        <v>9501.0</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>56</v>
       </c>
@@ -808,11 +841,61 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="3">
+        <v>1214.0</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="3">
+        <v>5062.0</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="3">
+        <v>1086.0</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="3">
+        <v>3019.0</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="3">
+        <v>3662.0</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="36" ht="14.25" customHeight="1"/>
     <row r="37" ht="14.25" customHeight="1"/>
     <row r="38" ht="14.25" customHeight="1"/>

--- a/data/faculty.xlsx
+++ b/data/faculty.xlsx
@@ -198,13 +198,13 @@
     <t>RIMT_FDP_726_029</t>
   </si>
   <si>
-    <t>DEERAJ GARG</t>
+    <t>DHEERAJ GARG</t>
   </si>
   <si>
     <t>RIMT_FDP_726_030</t>
   </si>
   <si>
-    <t>DEEPSHIKA</t>
+    <t>DEEPSHIKHA</t>
   </si>
   <si>
     <t>RIMT_FDP_726_031</t>

--- a/data/faculty.xlsx
+++ b/data/faculty.xlsx
@@ -204,7 +204,7 @@
     <t>RIMT_FDP_726_030</t>
   </si>
   <si>
-    <t>DEEPSHIKHA</t>
+    <t>DEEP SHIKHA</t>
   </si>
   <si>
     <t>RIMT_FDP_726_031</t>

--- a/data/faculty.xlsx
+++ b/data/faculty.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
   <si>
     <t>Employee Code</t>
   </si>
@@ -226,6 +226,18 @@
   </si>
   <si>
     <t>RIMT_FDP_726_034</t>
+  </si>
+  <si>
+    <t>ROHAN VERMA</t>
+  </si>
+  <si>
+    <t>RIMT_FDP_726_035</t>
+  </si>
+  <si>
+    <t>PRANAV BANSAL</t>
+  </si>
+  <si>
+    <t>RIMT_FDP_726_036</t>
   </si>
 </sst>
 </file>
@@ -896,8 +908,28 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="3">
+        <v>3969.0</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="3">
+        <v>2519.0</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1"/>
